--- a/data/trans_camb/P42-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P42-Provincia-trans_camb.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -515,9 +515,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -529,25 +526,18 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -578,21 +568,6 @@
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2023/2007</t>
         </is>
@@ -607,9 +582,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -624,17 +596,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9,37</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6,09</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14,79</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -648,21 +620,6 @@
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>14,79</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,37</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6,09</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>14,79</t>
         </is>
@@ -677,47 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,86; 15,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,89; 12,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,54; 20,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,96; 15,64</t>
+          <t>2,86; 15,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,46</t>
+          <t>-0,89; 12,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,52; 20,95</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>2,96; 15,64</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 13,46</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>5,52; 20,95</t>
+          <t>4,54; 20,93</t>
         </is>
       </c>
     </row>
@@ -730,17 +672,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -754,21 +696,6 @@
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>18,73%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>11,87%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>7,72%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>18,73%</t>
         </is>
@@ -783,47 +710,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,59; 21,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,08; 16,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,23; 28,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,54; 20,91</t>
+          <t>3,59; 21,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 18,25</t>
+          <t>-1,08; 16,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,01; 28,54</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,54; 20,91</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0,13; 18,25</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>7,01; 28,54</t>
+          <t>6,23; 28,13</t>
         </is>
       </c>
     </row>
@@ -840,17 +752,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9,08</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2,64</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8,91</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -864,21 +776,6 @@
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>8,91</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,08</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2,64</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>8,91</t>
         </is>
@@ -893,47 +790,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,91; 13,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,57; 7,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,7; 13,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,09; 12,91</t>
+          <t>4,91; 13,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 7,44</t>
+          <t>-2,57; 7,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,75; 13,4</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>5,09; 12,91</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-2,22; 7,44</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>3,75; 13,4</t>
+          <t>3,7; 13,1</t>
         </is>
       </c>
     </row>
@@ -946,17 +828,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -970,21 +852,6 @@
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10,91%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,12%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3,23%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>10,91%</t>
         </is>
@@ -999,47 +866,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,77; 17,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,01; 9,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,57; 16,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,13; 16,36</t>
+          <t>5,77; 17,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 9,4</t>
+          <t>-3,01; 9,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,42; 16,92</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>6,13; 16,36</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-2,61; 9,4</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>4,42; 16,92</t>
+          <t>4,57; 16,78</t>
         </is>
       </c>
     </row>
@@ -1056,17 +908,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9,36</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10,64</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4,14</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1080,21 +932,6 @@
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,14</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>9,36</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>10,64</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>4,14</t>
         </is>
@@ -1109,47 +946,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,81; 15,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,87; 16,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,46; 11,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,29; 15,6</t>
+          <t>3,81; 15,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,25; 16,15</t>
+          <t>4,87; 16,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 10,99</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,29; 15,6</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4,25; 16,15</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>-2,31; 10,99</t>
+          <t>-2,46; 11,42</t>
         </is>
       </c>
     </row>
@@ -1162,17 +984,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1186,21 +1008,6 @@
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>5,45%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>12,32%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>14,0%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>5,45%</t>
         </is>
@@ -1215,47 +1022,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,81; 21,64</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,13; 23,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,08; 15,48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,25; 21,79</t>
+          <t>4,81; 21,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,37; 22,53</t>
+          <t>6,13; 23,51</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 15,33</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>4,25; 21,79</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>5,37; 22,53</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>-3,02; 15,33</t>
+          <t>-3,08; 15,48</t>
         </is>
       </c>
     </row>
@@ -1272,17 +1064,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8,11</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8,22</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15,29</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1296,21 +1088,6 @@
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>15,29</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>8,11</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>8,22</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>15,29</t>
         </is>
@@ -1325,47 +1102,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,37; 14,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,61; 13,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,28; 21,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,23; 13,5</t>
+          <t>3,37; 14,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,72; 14,23</t>
+          <t>2,61; 13,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,19; 21,34</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>2,23; 13,5</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>2,72; 14,23</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>9,19; 21,34</t>
+          <t>9,28; 21,94</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1140,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1402,21 +1164,6 @@
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>20,0%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>10,61%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>10,76%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>20,0%</t>
         </is>
@@ -1431,47 +1178,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,3; 20,34</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,37; 19,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>11,69; 30,32</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,87; 18,6</t>
+          <t>4,3; 20,34</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,51; 19,55</t>
+          <t>3,37; 19,25</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,39; 29,47</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2,87; 18,6</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>3,51; 19,55</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>11,39; 29,47</t>
+          <t>11,69; 30,32</t>
         </is>
       </c>
     </row>
@@ -1488,17 +1220,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12,34</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16,25</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13,05</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1512,21 +1244,6 @@
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>13,05</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>12,34</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>16,25</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>13,05</t>
         </is>
@@ -1541,47 +1258,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,92; 20,28</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,26; 23,47</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,09; 20,72</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,62; 20,21</t>
+          <t>4,92; 20,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,84; 23,69</t>
+          <t>9,26; 23,47</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,9; 20,47</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>4,62; 20,21</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>8,84; 23,69</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>4,9; 20,47</t>
+          <t>5,09; 20,72</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1296,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1618,21 +1320,6 @@
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>17,79%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>16,81%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>22,15%</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>17,79%</t>
         </is>
@@ -1647,47 +1334,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,66; 29,98</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12,29; 35,11</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,9; 30,62</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6,02; 29,58</t>
+          <t>6,66; 29,98</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>11,26; 35,05</t>
+          <t>12,29; 35,11</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,33; 30,07</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>6,02; 29,58</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>11,26; 35,05</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>6,33; 30,07</t>
+          <t>6,9; 30,62</t>
         </is>
       </c>
     </row>
@@ -1704,17 +1376,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12,46</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4,96</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3,14</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1728,21 +1400,6 @@
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>-3,14</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>12,46</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>4,96</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>-3,14</t>
         </is>
@@ -1757,47 +1414,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,98; 18,97</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,76; 11,68</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-11,01; 3,87</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5,7; 18,87</t>
+          <t>5,98; 18,97</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 12,25</t>
+          <t>-2,76; 11,68</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-10,53; 4,33</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>5,7; 18,87</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>-2,09; 12,25</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>-10,53; 4,33</t>
+          <t>-11,01; 3,87</t>
         </is>
       </c>
     </row>
@@ -1810,17 +1452,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-4,26%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1834,21 +1476,6 @@
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>-4,26%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>16,92%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>6,73%</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>-4,26%</t>
         </is>
@@ -1863,47 +1490,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,56; 27,14</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,53; 16,7</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-13,91; 5,5</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7,28; 27,1</t>
+          <t>7,56; 27,14</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 17,46</t>
+          <t>-3,53; 16,7</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-13,8; 6,16</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>7,28; 27,1</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>-2,76; 17,46</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>-13,8; 6,16</t>
+          <t>-13,91; 5,5</t>
         </is>
       </c>
     </row>
@@ -1920,17 +1532,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5,93</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8,06</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-23,78</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1944,21 +1556,6 @@
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>-23,78</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>5,93</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>8,06</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>-23,78</t>
         </is>
@@ -1973,47 +1570,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,08; 9,4</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,04; 11,67</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-58,01; 4,8</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2,03; 9,69</t>
+          <t>2,08; 9,4</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>4,04; 11,78</t>
+          <t>4,04; 11,67</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-58,5; 5,15</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>2,03; 9,69</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>4,04; 11,78</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>-58,5; 5,15</t>
+          <t>-58,01; 4,8</t>
         </is>
       </c>
     </row>
@@ -2026,17 +1608,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-28,4%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2050,21 +1632,6 @@
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>-28,4%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>7,08%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>9,63%</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>-28,4%</t>
         </is>
@@ -2079,47 +1646,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,41; 11,57</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,86; 14,42</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-68,48; 5,74</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2,24; 11,88</t>
+          <t>2,41; 11,57</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>4,7; 14,55</t>
+          <t>4,86; 14,42</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-69,49; 6,21</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>2,24; 11,88</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>4,7; 14,55</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>-69,49; 6,21</t>
+          <t>-68,48; 5,74</t>
         </is>
       </c>
     </row>
@@ -2136,17 +1688,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5,33</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9,76</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-2,03</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2160,21 +1712,6 @@
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>-2,03</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>5,33</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>9,76</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>-2,03</t>
         </is>
@@ -2189,47 +1726,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,45; 8,96</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,32; 13,33</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,71; 2,12</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1,28; 9,11</t>
+          <t>1,45; 8,96</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>6,14; 13,23</t>
+          <t>6,32; 13,33</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 2,87</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>1,28; 9,11</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>6,14; 13,23</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>-6,28; 2,87</t>
+          <t>-6,71; 2,12</t>
         </is>
       </c>
     </row>
@@ -2242,17 +1764,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-2,55%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2266,21 +1788,6 @@
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>-2,55%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>6,67%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>12,23%</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>-2,55%</t>
         </is>
@@ -2295,47 +1802,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,78; 11,57</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,7; 17,25</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,28; 2,71</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1,55; 11,75</t>
+          <t>1,78; 11,57</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>7,4; 16,98</t>
+          <t>7,7; 17,25</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 3,49</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>1,55; 11,75</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>7,4; 16,98</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>-7,69; 3,49</t>
+          <t>-8,28; 2,71</t>
         </is>
       </c>
     </row>
@@ -2352,17 +1844,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8,05</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8,08</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,56</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2376,21 +1868,6 @@
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>-0,56</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>8,05</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>8,08</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>-0,56</t>
         </is>
@@ -2405,47 +1882,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,18; 9,9</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,17; 9,88</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-17,73; 6,29</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>6,43; 9,98</t>
+          <t>6,18; 9,9</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>6,4; 9,93</t>
+          <t>6,17; 9,88</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-19,42; 6,21</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>6,43; 9,98</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>6,4; 9,93</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>-19,42; 6,21</t>
+          <t>-17,73; 6,29</t>
         </is>
       </c>
     </row>
@@ -2458,17 +1920,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-0,71%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2482,21 +1944,6 @@
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>-0,71%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>10,18%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>10,21%</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>-0,71%</t>
         </is>
@@ -2511,47 +1958,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,63; 12,72</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,69; 12,62</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-22,6; 8,01</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>8,02; 12,86</t>
+          <t>7,63; 12,72</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>8,01; 12,81</t>
+          <t>7,69; 12,62</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-24,65; 7,89</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>8,02; 12,86</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>8,01; 12,81</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>-24,65; 7,89</t>
+          <t>-22,6; 8,01</t>
         </is>
       </c>
     </row>
@@ -2563,7 +1995,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="12">
     <mergeCell ref="A32:A35"/>
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="C1:E1"/>
@@ -2571,7 +2003,6 @@
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A12:A15"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A28:A31"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>

--- a/data/trans_camb/P42-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P42-Provincia-trans_camb.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14,79</t>
+          <t>15,69</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,79</t>
+          <t>15,69</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,86; 15,82</t>
+          <t>2,82; 15,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 12,23</t>
+          <t>-1,17; 13,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,54; 20,93</t>
+          <t>9,36; 22,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,86; 15,82</t>
+          <t>2,82; 15,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 12,23</t>
+          <t>-1,17; 13,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,54; 20,93</t>
+          <t>9,36; 22,37</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>19,88%</t>
         </is>
       </c>
     </row>
@@ -710,32 +710,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,59; 21,46</t>
+          <t>3,3; 20,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 16,39</t>
+          <t>-1,21; 17,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,23; 28,13</t>
+          <t>11,45; 30,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,59; 21,46</t>
+          <t>3,3; 20,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 16,39</t>
+          <t>-1,21; 17,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,23; 28,13</t>
+          <t>11,45; 30,37</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8,91</t>
+          <t>8,15</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,91</t>
+          <t>8,15</t>
         </is>
       </c>
     </row>
@@ -790,32 +790,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,91; 13,66</t>
+          <t>4,92; 13,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 7,32</t>
+          <t>-2,15; 7,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,7; 13,1</t>
+          <t>3,09; 12,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,91; 13,66</t>
+          <t>4,92; 13,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 7,32</t>
+          <t>-2,15; 7,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,7; 13,1</t>
+          <t>3,09; 12,83</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -866,32 +866,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,77; 17,34</t>
+          <t>5,86; 16,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 9,25</t>
+          <t>-2,55; 9,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,57; 16,78</t>
+          <t>3,73; 16,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,77; 17,34</t>
+          <t>5,86; 16,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 9,25</t>
+          <t>-2,55; 9,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,57; 16,78</t>
+          <t>3,73; 16,43</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,14</t>
+          <t>4,39</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,14</t>
+          <t>4,39</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,81; 15,51</t>
+          <t>2,66; 15,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,87; 16,83</t>
+          <t>4,48; 16,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 11,42</t>
+          <t>-2,94; 10,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,81; 15,51</t>
+          <t>2,66; 15,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,87; 16,83</t>
+          <t>4,48; 16,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 11,42</t>
+          <t>-2,94; 10,77</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -1022,32 +1022,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,81; 21,64</t>
+          <t>3,39; 20,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,13; 23,51</t>
+          <t>5,54; 22,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 15,48</t>
+          <t>-3,56; 14,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,81; 21,64</t>
+          <t>3,39; 20,82</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,13; 23,51</t>
+          <t>5,54; 22,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 15,48</t>
+          <t>-3,56; 14,86</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15,29</t>
+          <t>11,72</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,29</t>
+          <t>11,72</t>
         </is>
       </c>
     </row>
@@ -1102,32 +1102,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,37; 14,74</t>
+          <t>2,28; 14,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,61; 13,95</t>
+          <t>2,75; 13,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,28; 21,94</t>
+          <t>5,27; 17,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,37; 14,74</t>
+          <t>2,28; 14,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,61; 13,95</t>
+          <t>2,75; 13,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,28; 21,94</t>
+          <t>5,27; 17,91</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>15,34%</t>
         </is>
       </c>
     </row>
@@ -1178,32 +1178,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,3; 20,34</t>
+          <t>2,84; 20,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,37; 19,25</t>
+          <t>3,69; 18,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11,69; 30,32</t>
+          <t>6,74; 24,59</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,3; 20,34</t>
+          <t>2,84; 20,02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,37; 19,25</t>
+          <t>3,69; 18,62</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,69; 30,32</t>
+          <t>6,74; 24,59</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13,05</t>
+          <t>12,18</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,05</t>
+          <t>12,18</t>
         </is>
       </c>
     </row>
@@ -1258,32 +1258,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,92; 20,28</t>
+          <t>4,06; 19,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9,26; 23,47</t>
+          <t>8,07; 23,5</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,09; 20,72</t>
+          <t>4,6; 20,34</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,92; 20,28</t>
+          <t>4,06; 19,68</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,26; 23,47</t>
+          <t>8,07; 23,5</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,09; 20,72</t>
+          <t>4,6; 20,34</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>16,6%</t>
         </is>
       </c>
     </row>
@@ -1334,32 +1334,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>6,66; 29,98</t>
+          <t>5,31; 28,67</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>12,29; 35,11</t>
+          <t>10,09; 35,12</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6,9; 30,62</t>
+          <t>5,86; 29,43</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6,66; 29,98</t>
+          <t>5,31; 28,67</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>12,29; 35,11</t>
+          <t>10,09; 35,12</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,9; 30,62</t>
+          <t>5,86; 29,43</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-3,14</t>
+          <t>-2,45</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-3,14</t>
+          <t>-2,45</t>
         </is>
       </c>
     </row>
@@ -1414,32 +1414,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>5,98; 18,97</t>
+          <t>5,97; 18,7</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 11,68</t>
+          <t>-2,57; 11,36</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-11,01; 3,87</t>
+          <t>-9,76; 5,39</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5,98; 18,97</t>
+          <t>5,97; 18,7</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 11,68</t>
+          <t>-2,57; 11,36</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-11,01; 3,87</t>
+          <t>-9,76; 5,39</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-4,26%</t>
+          <t>-3,32%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-4,26%</t>
+          <t>-3,32%</t>
         </is>
       </c>
     </row>
@@ -1490,32 +1490,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>7,56; 27,14</t>
+          <t>7,85; 27,11</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 16,7</t>
+          <t>-3,23; 16,49</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-13,91; 5,5</t>
+          <t>-12,61; 7,65</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7,56; 27,14</t>
+          <t>7,85; 27,11</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 16,7</t>
+          <t>-3,23; 16,49</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-13,91; 5,5</t>
+          <t>-12,61; 7,65</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-23,78</t>
+          <t>3,67</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-23,78</t>
+          <t>3,67</t>
         </is>
       </c>
     </row>
@@ -1570,32 +1570,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2,08; 9,4</t>
+          <t>2,53; 9,93</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>4,04; 11,67</t>
+          <t>4,61; 11,65</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-58,01; 4,8</t>
+          <t>-0,69; 8,19</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2,08; 9,4</t>
+          <t>2,53; 9,93</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>4,04; 11,67</t>
+          <t>4,61; 11,65</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-58,01; 4,8</t>
+          <t>-0,69; 8,19</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-28,4%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-28,4%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -1646,32 +1646,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2,41; 11,57</t>
+          <t>2,94; 12,29</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>4,86; 14,42</t>
+          <t>5,4; 14,58</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-68,48; 5,74</t>
+          <t>-0,79; 10,04</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2,41; 11,57</t>
+          <t>2,94; 12,29</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>4,86; 14,42</t>
+          <t>5,4; 14,58</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-68,48; 5,74</t>
+          <t>-0,79; 10,04</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-2,03</t>
+          <t>-3,56</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-2,03</t>
+          <t>-3,56</t>
         </is>
       </c>
     </row>
@@ -1726,32 +1726,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>1,45; 8,96</t>
+          <t>1,69; 9,15</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>6,32; 13,33</t>
+          <t>6,39; 13,6</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 2,12</t>
+          <t>-8,1; 1,39</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1,45; 8,96</t>
+          <t>1,69; 9,15</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>6,32; 13,33</t>
+          <t>6,39; 13,6</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 2,12</t>
+          <t>-8,1; 1,39</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-2,55%</t>
+          <t>-4,46%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-2,55%</t>
+          <t>-4,46%</t>
         </is>
       </c>
     </row>
@@ -1802,32 +1802,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>1,78; 11,57</t>
+          <t>2,11; 11,89</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>7,7; 17,25</t>
+          <t>7,84; 17,76</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 2,71</t>
+          <t>-9,84; 1,77</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1,78; 11,57</t>
+          <t>2,11; 11,89</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>7,7; 17,25</t>
+          <t>7,84; 17,76</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 2,71</t>
+          <t>-9,84; 1,77</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-0,56</t>
+          <t>4,6</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-0,56</t>
+          <t>4,6</t>
         </is>
       </c>
     </row>
@@ -1882,32 +1882,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>6,18; 9,9</t>
+          <t>6,34; 9,88</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>6,17; 9,88</t>
+          <t>6,38; 9,9</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-17,73; 6,29</t>
+          <t>2,75; 6,73</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>6,18; 9,9</t>
+          <t>6,34; 9,88</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>6,17; 9,88</t>
+          <t>6,38; 9,9</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-17,73; 6,29</t>
+          <t>2,75; 6,73</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-0,71%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-0,71%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -1958,32 +1958,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>7,63; 12,72</t>
+          <t>7,86; 12,61</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>7,69; 12,62</t>
+          <t>7,94; 12,67</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-22,6; 8,01</t>
+          <t>3,46; 8,63</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>7,63; 12,72</t>
+          <t>7,86; 12,61</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>7,69; 12,62</t>
+          <t>7,94; 12,67</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-22,6; 8,01</t>
+          <t>3,46; 8,63</t>
         </is>
       </c>
     </row>
